--- a/data/dividends_info_20260322.xlsx
+++ b/data/dividends_info_20260322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>25.85000038146973</v>
+        <v>25.75</v>
       </c>
       <c r="I15" t="n">
-        <v>4.294003805105127</v>
+        <v>4.310679611650485</v>
       </c>
       <c r="J15" t="n">
         <v>74</v>
@@ -1290,11 +1290,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.104</v>
+        <v>2.2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1313,19 +1313,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IT0001233417</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.339999914169312</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>4.444444607465701</v>
+        <v>4.369414233707984</v>
       </c>
       <c r="J19" t="n">
         <v>57</v>
@@ -1337,11 +1337,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1365,30 +1365,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IT0004056880</t>
+          <t>IT0005508921</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>8.369999885559082</v>
+        <v>7.065000057220459</v>
       </c>
       <c r="I20" t="n">
-        <v>3.464755125031034</v>
+        <v>12.17268213778819</v>
       </c>
       <c r="J20" t="n">
         <v>57</v>
       </c>
       <c r="K20" t="n">
-        <v>59</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.077</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1407,19 +1407,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IT0001469383</t>
+          <t>IT0000066123</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.96399998664856</v>
+        <v>10.46500015258789</v>
       </c>
       <c r="I21" t="n">
-        <v>3.920570291418157</v>
+        <v>5.35117049053762</v>
       </c>
       <c r="J21" t="n">
         <v>57</v>
@@ -1431,11 +1431,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.64</v>
+        <v>0.04</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1459,14 +1459,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IT0000062072</t>
+          <t>IT0001472171</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>33.34999847412109</v>
+        <v>1.754999995231628</v>
       </c>
       <c r="I22" t="n">
-        <v>4.917541454379993</v>
+        <v>2.279202285394919</v>
       </c>
       <c r="J22" t="n">
         <v>57</v>
@@ -1478,11 +1478,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IT0003261697</t>
+          <t>IT0003127930</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>31.68000030517578</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I23" t="n">
-        <v>6.313131252316453</v>
+        <v>3.440366867124189</v>
       </c>
       <c r="J23" t="n">
         <v>57</v>
@@ -1525,11 +1525,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1</v>
+        <v>0.108</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1553,14 +1553,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NL0015000N33</t>
+          <t>IT0005244618</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.579999923706055</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I24" t="n">
-        <v>2.79329614891385</v>
+        <v>4.716157283802238</v>
       </c>
       <c r="J24" t="n">
         <v>57</v>
@@ -1572,11 +1572,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.14846</v>
+        <v>2.06</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1600,14 +1600,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IT0005119810</t>
+          <t>IT0001128047</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>35</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4241714285714286</v>
+        <v>3.393739660803659</v>
       </c>
       <c r="J25" t="n">
         <v>57</v>
@@ -1619,11 +1619,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1647,14 +1647,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IT0003188064</t>
+          <t>IT0003121677</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>21.79999923706055</v>
+        <v>14.07999992370605</v>
       </c>
       <c r="I26" t="n">
-        <v>4.220183633933238</v>
+        <v>5.326704574317849</v>
       </c>
       <c r="J26" t="n">
         <v>57</v>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1694,14 +1694,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NL0015001KT6</t>
+          <t>NL0013995087</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7.474999904632568</v>
+        <v>14.46000003814697</v>
       </c>
       <c r="I27" t="n">
-        <v>4.013377977624823</v>
+        <v>2.074688791207255</v>
       </c>
       <c r="J27" t="n">
         <v>57</v>
@@ -1713,11 +1713,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.04</v>
+        <v>0.85</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1741,14 +1741,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>IT0004764699</t>
+          <t>IT0005246191</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>72.33999633789062</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="I28" t="n">
-        <v>1.437655588399945</v>
+        <v>2.162849914761413</v>
       </c>
       <c r="J28" t="n">
         <v>57</v>
@@ -1760,11 +1760,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.2</v>
+        <v>0.85</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1783,19 +1783,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IT0001031084</t>
+          <t>IT0003115950</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>50.34999847412109</v>
+        <v>29.44000053405762</v>
       </c>
       <c r="I29" t="n">
-        <v>4.369414233707984</v>
+        <v>2.887228208493675</v>
       </c>
       <c r="J29" t="n">
         <v>57</v>
@@ -1807,11 +1807,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.86</v>
+        <v>0.2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1825,40 +1825,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IT0005508921</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7.065000057220459</v>
+        <v>5.389999866485596</v>
       </c>
       <c r="I30" t="n">
-        <v>12.17268213778819</v>
+        <v>3.710575231060341</v>
       </c>
       <c r="J30" t="n">
         <v>57</v>
       </c>
       <c r="K30" t="n">
-        <v>-2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1882,14 +1882,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IT0000066123</t>
+          <t>IT0001157020</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>10.46500015258789</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>5.35117049053762</v>
+        <v>4.504504349699816</v>
       </c>
       <c r="J31" t="n">
         <v>57</v>
@@ -1901,11 +1901,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.04</v>
+        <v>0.215</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1929,14 +1929,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IT0001472171</t>
+          <t>IT0004356751</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.754999995231628</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="I32" t="n">
-        <v>2.279202285394919</v>
+        <v>5.023364239732766</v>
       </c>
       <c r="J32" t="n">
         <v>57</v>
@@ -1948,11 +1948,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3</v>
+        <v>0.79</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1976,14 +1976,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IT0003127930</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8.720000267028809</v>
+        <v>18.23500061035156</v>
       </c>
       <c r="I33" t="n">
-        <v>3.440366867124189</v>
+        <v>4.332327795764023</v>
       </c>
       <c r="J33" t="n">
         <v>57</v>
@@ -1995,11 +1995,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.108</v>
+        <v>0.093</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2023,14 +2023,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IT0005244618</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.289999961853027</v>
+        <v>4.570000171661377</v>
       </c>
       <c r="I34" t="n">
-        <v>4.716157283802238</v>
+        <v>2.035010864478607</v>
       </c>
       <c r="J34" t="n">
         <v>57</v>
@@ -2042,11 +2042,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.06</v>
+        <v>0.06</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2070,14 +2070,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>IT0001128047</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>60.70000076293945</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I35" t="n">
-        <v>3.393739660803659</v>
+        <v>3.125000069849194</v>
       </c>
       <c r="J35" t="n">
         <v>57</v>
@@ -2089,11 +2089,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.75</v>
+        <v>0.103</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2117,30 +2117,30 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>IT0003121677</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>14.07999992370605</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="I36" t="n">
-        <v>5.326704574317849</v>
+        <v>1.896869304902246</v>
       </c>
       <c r="J36" t="n">
         <v>57</v>
       </c>
       <c r="K36" t="n">
-        <v>59</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2164,14 +2164,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NL0013995087</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14.57999992370605</v>
+        <v>4.966000080108643</v>
       </c>
       <c r="I37" t="n">
-        <v>2.057613179491319</v>
+        <v>3.826016853303058</v>
       </c>
       <c r="J37" t="n">
         <v>57</v>
@@ -2183,11 +2183,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.85</v>
+        <v>0.432</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>IT0005246191</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>39.29999923706055</v>
+        <v>9.725000381469727</v>
       </c>
       <c r="I38" t="n">
-        <v>2.162849914761413</v>
+        <v>4.442159208786708</v>
       </c>
       <c r="J38" t="n">
         <v>57</v>
@@ -2230,11 +2230,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.85</v>
+        <v>0.44</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2258,14 +2258,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IT0003115950</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>29.44000053405762</v>
+        <v>24.6200008392334</v>
       </c>
       <c r="I39" t="n">
-        <v>2.887228208493675</v>
+        <v>1.787164845660096</v>
       </c>
       <c r="J39" t="n">
         <v>57</v>
@@ -2277,11 +2277,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2300,19 +2300,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IT0005312027</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.389999866485596</v>
+        <v>6.510000228881836</v>
       </c>
       <c r="I40" t="n">
-        <v>3.710575231060341</v>
+        <v>7.219661804539254</v>
       </c>
       <c r="J40" t="n">
         <v>57</v>
@@ -2324,11 +2324,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2352,14 +2352,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>IT0001157020</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>22.20000076293945</v>
+        <v>52.09999847412109</v>
       </c>
       <c r="I41" t="n">
-        <v>4.504504349699816</v>
+        <v>2.687140193862774</v>
       </c>
       <c r="J41" t="n">
         <v>57</v>
@@ -2371,11 +2371,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.215</v>
+        <v>0.3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2399,14 +2399,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>IT0004356751</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4.28000020980835</v>
+        <v>2.844000101089478</v>
       </c>
       <c r="I42" t="n">
-        <v>5.023364239732766</v>
+        <v>10.54852283180567</v>
       </c>
       <c r="J42" t="n">
         <v>57</v>
@@ -2418,11 +2418,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.79</v>
+        <v>1.35</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>18.23500061035156</v>
+        <v>78.75</v>
       </c>
       <c r="I43" t="n">
-        <v>4.332327795764023</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="J43" t="n">
         <v>57</v>
@@ -2465,11 +2465,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.093</v>
+        <v>0.17</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2493,14 +2493,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4.570000171661377</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I44" t="n">
-        <v>2.035010864478607</v>
+        <v>4.970760123029561</v>
       </c>
       <c r="J44" t="n">
         <v>57</v>
@@ -2512,11 +2512,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.919999957084656</v>
+        <v>4.380000114440918</v>
       </c>
       <c r="I45" t="n">
-        <v>3.125000069849194</v>
+        <v>0.9132419852711756</v>
       </c>
       <c r="J45" t="n">
         <v>57</v>
@@ -2559,11 +2559,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.103</v>
+        <v>1.05</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2587,30 +2587,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5.429999828338623</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="I46" t="n">
-        <v>1.896869304902246</v>
+        <v>3.671328622360115</v>
       </c>
       <c r="J46" t="n">
         <v>57</v>
       </c>
       <c r="K46" t="n">
-        <v>-306</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2634,14 +2634,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.966000080108643</v>
+        <v>17.22999954223633</v>
       </c>
       <c r="I47" t="n">
-        <v>3.826016853303058</v>
+        <v>2.205455659290626</v>
       </c>
       <c r="J47" t="n">
         <v>57</v>
@@ -2653,15 +2653,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.432</v>
+        <v>0.6</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2681,14 +2681,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.725000381469727</v>
+        <v>24.48999977111816</v>
       </c>
       <c r="I48" t="n">
-        <v>4.442159208786708</v>
+        <v>2.449979606400809</v>
       </c>
       <c r="J48" t="n">
         <v>57</v>
@@ -2700,11 +2700,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2728,14 +2728,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>24.6200008392334</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="I49" t="n">
-        <v>1.787164845660096</v>
+        <v>1.134521866036118</v>
       </c>
       <c r="J49" t="n">
         <v>57</v>
@@ -2747,11 +2747,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2775,14 +2775,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0003865570</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.510000228881836</v>
+        <v>2.236000061035156</v>
       </c>
       <c r="I50" t="n">
-        <v>7.219661804539254</v>
+        <v>11.62790665934208</v>
       </c>
       <c r="J50" t="n">
         <v>57</v>
@@ -2794,11 +2794,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2822,30 +2822,30 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>52.09999847412109</v>
+        <v>9.939999580383301</v>
       </c>
       <c r="I51" t="n">
-        <v>2.687140193862774</v>
+        <v>3.521126909207611</v>
       </c>
       <c r="J51" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2869,30 +2869,30 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.844000101089478</v>
+        <v>13.92000007629395</v>
       </c>
       <c r="I52" t="n">
-        <v>10.54852283180567</v>
+        <v>3.591954003301412</v>
       </c>
       <c r="J52" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.35</v>
+        <v>0.22</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2916,30 +2916,30 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>78.75</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="I53" t="n">
-        <v>1.714285714285714</v>
+        <v>3.389830628023214</v>
       </c>
       <c r="J53" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2948,12 +2948,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2963,30 +2963,30 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0004093263</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3.420000076293945</v>
+        <v>3.365000009536743</v>
       </c>
       <c r="I54" t="n">
-        <v>4.970760123029561</v>
+        <v>4.754829109852724</v>
       </c>
       <c r="J54" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K54" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.04</v>
+        <v>0.61</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3010,30 +3010,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4.380000114440918</v>
+        <v>19.31999969482422</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9132419852711756</v>
+        <v>3.157349946353351</v>
       </c>
       <c r="J55" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K55" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3057,30 +3057,30 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>28.60000038146973</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="I56" t="n">
-        <v>3.671328622360115</v>
+        <v>5.907172805619612</v>
       </c>
       <c r="J56" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K56" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.38</v>
+        <v>0.5105</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3104,30 +3104,30 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>17.22999954223633</v>
+        <v>8.409999847412109</v>
       </c>
       <c r="I57" t="n">
-        <v>2.205455659290626</v>
+        <v>6.070154688018085</v>
       </c>
       <c r="J57" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K57" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3151,26 +3151,26 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>24.48999977111816</v>
+        <v>6.945000171661377</v>
       </c>
       <c r="I58" t="n">
-        <v>2.449979606400809</v>
+        <v>3.887688888788189</v>
       </c>
       <c r="J58" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K58" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3198,30 +3198,30 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>30.85000038146973</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="I59" t="n">
-        <v>1.134521866036118</v>
+        <v>7.726268957828755</v>
       </c>
       <c r="J59" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K59" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3230,45 +3230,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>IT0003865570</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.236000061035156</v>
+        <v>18.5</v>
       </c>
       <c r="I60" t="n">
-        <v>11.62790665934208</v>
+        <v>4.054054054054054</v>
       </c>
       <c r="J60" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K60" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3292,30 +3292,30 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>9.939999580383301</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I61" t="n">
-        <v>3.521126909207611</v>
+        <v>4.174757204245461</v>
       </c>
       <c r="J61" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K61" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3339,30 +3339,30 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>13.92000007629395</v>
+        <v>3.904999971389771</v>
       </c>
       <c r="I62" t="n">
-        <v>3.591954003301412</v>
+        <v>3.841229221484878</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K62" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.22</v>
+        <v>0.197169</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>6.489999771118164</v>
+        <v>11.53999996185303</v>
       </c>
       <c r="I63" t="n">
-        <v>3.389830628023214</v>
+        <v>1.708570196289149</v>
       </c>
       <c r="J63" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K63" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.16</v>
+        <v>1.1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3433,14 +3433,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IT0004093263</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3.365000009536743</v>
+        <v>25</v>
       </c>
       <c r="I64" t="n">
-        <v>4.754829109852724</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>43</v>
@@ -3452,11 +3452,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>19.31999969482422</v>
+        <v>36</v>
       </c>
       <c r="I65" t="n">
-        <v>3.157349946353351</v>
+        <v>1.305555555555555</v>
       </c>
       <c r="J65" t="n">
         <v>43</v>
@@ -3499,11 +3499,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3527,14 +3527,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>11.85000038146973</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="I66" t="n">
-        <v>5.907172805619612</v>
+        <v>1.591511904131904</v>
       </c>
       <c r="J66" t="n">
         <v>43</v>
@@ -3546,11 +3546,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5105</v>
+        <v>0.27</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>8.409999847412109</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="I67" t="n">
-        <v>6.070154688018085</v>
+        <v>1.218961646275258</v>
       </c>
       <c r="J67" t="n">
         <v>43</v>
@@ -3593,15 +3593,15 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3621,14 +3621,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>6.945000171661377</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I68" t="n">
-        <v>3.887688888788189</v>
+        <v>3.762376095521527</v>
       </c>
       <c r="J68" t="n">
         <v>43</v>
@@ -3640,11 +3640,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>4.53000020980835</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I69" t="n">
-        <v>7.726268957828755</v>
+        <v>1.094890526192248</v>
       </c>
       <c r="J69" t="n">
         <v>43</v>
@@ -3687,11 +3687,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.75</v>
+        <v>0.16</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3700,45 +3700,45 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0001033700</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>18.5</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I70" t="n">
-        <v>4.054054054054054</v>
+        <v>2.707275873620561</v>
       </c>
       <c r="J70" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K70" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.43</v>
+        <v>0.065</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3762,30 +3762,30 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0003372205</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>10.30000019073486</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I71" t="n">
-        <v>4.174757204245461</v>
+        <v>3.037383028675626</v>
       </c>
       <c r="J71" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K71" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3809,30 +3809,30 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0003365613</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>3.904999971389771</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="I72" t="n">
-        <v>3.841229221484878</v>
+        <v>3.410641236045195</v>
       </c>
       <c r="J72" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K72" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.197169</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3856,30 +3856,30 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0005549255</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.53999996185303</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="I73" t="n">
-        <v>1.708570196289149</v>
+        <v>5.223880466891178</v>
       </c>
       <c r="J73" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K73" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3888,12 +3888,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3903,30 +3903,30 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>25</v>
+        <v>6.585000038146973</v>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>7.593014382741001</v>
       </c>
       <c r="J74" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K74" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3950,30 +3950,30 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0004776628</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>36</v>
+        <v>16.44000053405762</v>
       </c>
       <c r="I75" t="n">
-        <v>1.305555555555555</v>
+        <v>3.953771161098443</v>
       </c>
       <c r="J75" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K75" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.2</v>
+        <v>0.54</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3997,30 +3997,30 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0005218380</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>75.40000152587891</v>
+        <v>11.24499988555908</v>
       </c>
       <c r="I76" t="n">
-        <v>1.591511904131904</v>
+        <v>4.802134330774625</v>
       </c>
       <c r="J76" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K76" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4044,30 +4044,30 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>NL0015435975</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>22.14999961853027</v>
+        <v>5.912000179290771</v>
       </c>
       <c r="I77" t="n">
-        <v>1.218961646275258</v>
+        <v>1.691474914873843</v>
       </c>
       <c r="J77" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K77" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4091,30 +4091,30 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0005215329</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>10.10000038146973</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="I78" t="n">
-        <v>3.762376095521527</v>
+        <v>1.96078435039117</v>
       </c>
       <c r="J78" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K78" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.3</v>
+        <v>3.615</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4123,12 +4123,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4138,30 +4138,30 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>NL0011585146</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>27.39999961853027</v>
+        <v>273.7999877929688</v>
       </c>
       <c r="I79" t="n">
-        <v>1.094890526192248</v>
+        <v>1.320306852143999</v>
       </c>
       <c r="J79" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K79" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.16</v>
+        <v>1.36</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4185,30 +4185,30 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0005144784</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5.909999847412109</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="I80" t="n">
-        <v>2.707275873620561</v>
+        <v>5.190839543500142</v>
       </c>
       <c r="J80" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K80" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.065</v>
+        <v>0.585</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4217,12 +4217,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4232,30 +4232,30 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>IT0004931058</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.140000104904175</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="I81" t="n">
-        <v>3.037383028675626</v>
+        <v>4.814814965984045</v>
       </c>
       <c r="J81" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K81" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4279,30 +4279,30 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0000062957</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>7.329999923706055</v>
+        <v>15.625</v>
       </c>
       <c r="I82" t="n">
-        <v>3.410641236045195</v>
+        <v>4.032</v>
       </c>
       <c r="J82" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K82" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4311,12 +4311,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4326,30 +4326,30 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>IT0005549255</t>
+          <t>IT0004176001</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.340000033378601</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="I83" t="n">
-        <v>5.223880466891178</v>
+        <v>0.9584664380990019</v>
       </c>
       <c r="J83" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K83" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>1.7208</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4373,14 +4373,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0005239360</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>6.585000038146973</v>
+        <v>59.63000106811523</v>
       </c>
       <c r="I84" t="n">
-        <v>7.593014382741001</v>
+        <v>2.885795688707658</v>
       </c>
       <c r="J84" t="n">
         <v>29</v>
@@ -4392,11 +4392,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.65</v>
+        <v>0.14</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4405,12 +4405,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4420,30 +4420,30 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IT0004776628</t>
+          <t>IT0001214433</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>16.44000053405762</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I85" t="n">
-        <v>3.953771161098443</v>
+        <v>0.6140351082662987</v>
       </c>
       <c r="J85" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K85" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.54</v>
+        <v>0.06</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4467,30 +4467,30 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0005418204</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>11.24499988555908</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I86" t="n">
-        <v>4.802134330774625</v>
+        <v>4.137930898405571</v>
       </c>
       <c r="J86" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K86" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1</v>
+        <v>0.034</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4514,30 +4514,30 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0005379604</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.912000179290771</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I87" t="n">
-        <v>1.691474914873843</v>
+        <v>1.7616580789651</v>
       </c>
       <c r="J87" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K87" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4546,92 +4546,92 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8.159999847412109</v>
+        <v>23.6200008392334</v>
       </c>
       <c r="I88" t="n">
-        <v>1.96078435039117</v>
+        <v>1.10076202693496</v>
       </c>
       <c r="J88" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3.615</v>
+        <v>0.09</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NL0011585146</t>
+          <t>NL0000226223</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>273.7999877929688</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="I89" t="n">
-        <v>1.320306852143999</v>
+        <v>0.3343239217865197</v>
       </c>
       <c r="J89" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.36</v>
+        <v>0.65</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4640,504 +4640,34 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0005144784</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>26.20000076293945</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="I90" t="n">
-        <v>5.190839543500142</v>
+        <v>1.290963296322813</v>
       </c>
       <c r="J90" t="n">
-        <v>29</v>
+        <v>-27</v>
       </c>
       <c r="K90" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>IT0004931058</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
-        <v>12.14999961853027</v>
-      </c>
-      <c r="I91" t="n">
-        <v>4.814814965984045</v>
-      </c>
-      <c r="J91" t="n">
-        <v>29</v>
-      </c>
-      <c r="K91" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>IT0000062957</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>15.625</v>
-      </c>
-      <c r="I92" t="n">
-        <v>4.032</v>
-      </c>
-      <c r="J92" t="n">
-        <v>29</v>
-      </c>
-      <c r="K92" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>IT0004176001</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>93.90000152587891</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.9584664380990019</v>
-      </c>
-      <c r="J93" t="n">
-        <v>29</v>
-      </c>
-      <c r="K93" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1.7208</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>IT0005239360</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
-        <v>59.63000106811523</v>
-      </c>
-      <c r="I94" t="n">
-        <v>2.885795688707658</v>
-      </c>
-      <c r="J94" t="n">
-        <v>29</v>
-      </c>
-      <c r="K94" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>IT0001214433</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
-        <v>22.79999923706055</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0.6140351082662987</v>
-      </c>
-      <c r="J95" t="n">
-        <v>22</v>
-      </c>
-      <c r="K95" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>IT0005418204</t>
-        </is>
-      </c>
-      <c r="H96" t="n">
-        <v>1.450000047683716</v>
-      </c>
-      <c r="I96" t="n">
-        <v>4.137930898405571</v>
-      </c>
-      <c r="J96" t="n">
-        <v>22</v>
-      </c>
-      <c r="K96" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Confinvest F.L. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>IT0005379604</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>1.929999947547913</v>
-      </c>
-      <c r="I97" t="n">
-        <v>1.7616580789651</v>
-      </c>
-      <c r="J97" t="n">
-        <v>8</v>
-      </c>
-      <c r="K97" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>IT0003132476</t>
-        </is>
-      </c>
-      <c r="H98" t="n">
-        <v>23.6200008392334</v>
-      </c>
-      <c r="I98" t="n">
-        <v>1.10076202693496</v>
-      </c>
-      <c r="J98" t="n">
-        <v>1</v>
-      </c>
-      <c r="K98" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="H99" t="n">
-        <v>26.92000007629395</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0.3343239217865197</v>
-      </c>
-      <c r="J99" t="n">
-        <v>1</v>
-      </c>
-      <c r="K99" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>IT0001031084</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
-        <v>50.34999847412109</v>
-      </c>
-      <c r="I100" t="n">
-        <v>1.290963296322813</v>
-      </c>
-      <c r="J100" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K100" t="n">
         <v>-25</v>
       </c>
     </row>
@@ -5152,7 +4682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C306"/>
+  <dimension ref="A1:C296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6739,7 +6269,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6756,7 +6286,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6773,7 +6303,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6790,7 +6320,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6807,7 +6337,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6817,14 +6347,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6858,7 +6388,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6875,7 +6405,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6892,7 +6422,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6902,14 +6432,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6926,7 +6456,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6943,7 +6473,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6960,7 +6490,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6977,7 +6507,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,7 +6524,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7011,7 +6541,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7028,7 +6558,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7045,7 +6575,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7062,7 +6592,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7079,7 +6609,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7096,7 +6626,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7113,7 +6643,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7130,7 +6660,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7147,7 +6677,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7164,7 +6694,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7181,7 +6711,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7198,7 +6728,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7215,7 +6745,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7232,7 +6762,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7249,7 +6779,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7266,7 +6796,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7283,7 +6813,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7300,7 +6830,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7317,7 +6847,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7334,7 +6864,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7351,7 +6881,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7361,14 +6891,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7385,7 +6915,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7402,7 +6932,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7419,7 +6949,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7436,7 +6966,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7453,7 +6983,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7470,7 +7000,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7487,7 +7017,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7504,7 +7034,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7521,7 +7051,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7538,7 +7068,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7548,14 +7078,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7572,7 +7102,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7589,7 +7119,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7606,7 +7136,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7623,7 +7153,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7633,14 +7163,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7650,14 +7180,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7674,7 +7204,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7684,14 +7214,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7708,7 +7238,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7725,7 +7255,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7742,7 +7272,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7759,7 +7289,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7776,7 +7306,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7793,7 +7323,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7810,7 +7340,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7827,7 +7357,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7844,7 +7374,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7861,7 +7391,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7878,7 +7408,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7888,14 +7418,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7905,14 +7435,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7929,7 +7459,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7946,7 +7476,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7956,7 +7486,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7510,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7997,7 +7527,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8014,7 +7544,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8031,7 +7561,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8048,12 +7578,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8065,12 +7595,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8082,12 +7612,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8099,29 +7629,29 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8133,29 +7663,29 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8167,12 +7697,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8184,12 +7714,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8201,12 +7731,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8218,7 +7748,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8228,14 +7758,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8252,7 +7782,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8269,7 +7799,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8286,7 +7816,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8303,7 +7833,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8320,7 +7850,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8330,14 +7860,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8354,7 +7884,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8371,7 +7901,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8388,7 +7918,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8405,7 +7935,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8439,7 +7969,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8456,7 +7986,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8473,7 +8003,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8483,14 +8013,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8507,7 +8037,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8524,7 +8054,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8534,14 +8064,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8558,7 +8088,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8575,7 +8105,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -8585,14 +8115,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8609,7 +8139,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8619,14 +8149,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -8643,7 +8173,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8660,7 +8190,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8677,29 +8207,29 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8711,46 +8241,46 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8762,97 +8292,97 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8864,12 +8394,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8881,12 +8411,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8898,46 +8428,46 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8949,12 +8479,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8966,114 +8496,114 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -9085,97 +8615,97 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9187,29 +8717,29 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9221,75 +8751,75 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -9306,7 +8836,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -9316,14 +8846,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -9333,14 +8863,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -9374,7 +8904,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -9384,14 +8914,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -9401,14 +8931,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -9418,14 +8948,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -9435,36 +8965,36 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9476,97 +9006,97 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9578,12 +9108,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9595,24 +9125,24 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -9629,7 +9159,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -9639,14 +9169,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -9656,14 +9186,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -9673,14 +9203,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9697,7 +9227,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9707,14 +9237,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9731,7 +9261,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9748,7 +9278,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9758,14 +9288,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9775,87 +9305,87 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9867,46 +9397,46 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9918,29 +9448,29 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9952,63 +9482,63 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10020,29 +9550,29 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10054,63 +9584,63 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10122,29 +9652,29 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10156,24 +9686,24 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -10183,177 +9713,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>Moncler S.p.A.</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>Moncler S.p.A.</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
           <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Ecomembrane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10381,214 +9741,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ecomembrane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Moncler S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Moncler S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Moncler S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>